--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_4_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_4_bus.xlsx
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.019485521667468</v>
+        <v>1.019485521667526</v>
       </c>
       <c r="G2">
-        <v>149.9612089037749</v>
+        <v>-0.03879109617642213</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -561,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8902319386642066</v>
+        <v>0.8902319386646703</v>
       </c>
       <c r="G3">
-        <v>149.220203107533</v>
+        <v>-0.7797968923376516</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -584,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.84533394365662</v>
+        <v>0.8453339436572478</v>
       </c>
       <c r="G4">
-        <v>151.2672005251284</v>
+        <v>1.267200525268436</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.845333943671228</v>
+        <v>0.8453339436718406</v>
       </c>
       <c r="G5">
-        <v>1.267200529701651</v>
+        <v>1.267200529835314</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -618,22 +618,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>40.05035537883598</v>
+        <v>40.05035537881115</v>
       </c>
       <c r="C6">
-        <v>27.7477005644063</v>
+        <v>27.7477005643891</v>
       </c>
       <c r="D6">
-        <v>0.0007385329100661764</v>
+        <v>0.0007385329100534611</v>
       </c>
       <c r="E6">
-        <v>0.00600934383484958</v>
+        <v>0.006009343834854926</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>82.99362924199868</v>
+        <v>82.99362924212427</v>
       </c>
     </row>
   </sheetData>
@@ -746,22 +746,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100000023840732</v>
+        <v>1.092677014834793</v>
       </c>
       <c r="O2">
-        <v>1.077288330003198</v>
+        <v>1.069211965363453</v>
       </c>
       <c r="P2">
-        <v>1.076694580917778</v>
+        <v>1.092091632311565</v>
       </c>
       <c r="Q2">
-        <v>179.9999999999588</v>
+        <v>29.292118720256</v>
       </c>
       <c r="R2">
-        <v>59.26415433307589</v>
+        <v>-90.03597085293045</v>
       </c>
       <c r="S2">
-        <v>-59.31733393494763</v>
+        <v>150.6906508001329</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -805,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.100000023839416</v>
+        <v>1.067403370677813</v>
       </c>
       <c r="O3">
-        <v>0.987426252349625</v>
+        <v>0.9387871689804239</v>
       </c>
       <c r="P3">
-        <v>0.975690240473248</v>
+        <v>1.056556102277697</v>
       </c>
       <c r="Q3">
-        <v>179.9999999999191</v>
+        <v>26.08578027748498</v>
       </c>
       <c r="R3">
-        <v>55.41631504159002</v>
+        <v>-90.7380415080557</v>
       </c>
       <c r="S3">
-        <v>-56.42897648791691</v>
+        <v>153.6258711928603</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -864,22 +864,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.100000023839416</v>
+        <v>1.043533397671073</v>
       </c>
       <c r="O4">
-        <v>0.9397573997042074</v>
+        <v>0.8935122209237658</v>
       </c>
       <c r="P4">
-        <v>0.9588546236692685</v>
+        <v>1.060763956348718</v>
       </c>
       <c r="Q4">
-        <v>179.9999999999191</v>
+        <v>25.34206718832577</v>
       </c>
       <c r="R4">
-        <v>55.40861802099833</v>
+        <v>-88.77958335480669</v>
       </c>
       <c r="S4">
-        <v>-53.78696299967743</v>
+        <v>155.0979067105141</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.043533397640815</v>
+        <v>1.043533397641724</v>
       </c>
       <c r="O5">
-        <v>0.8935122209381459</v>
+        <v>0.8935122209391901</v>
       </c>
       <c r="P5">
-        <v>1.060763956382946</v>
+        <v>1.060763956384086</v>
       </c>
       <c r="Q5">
-        <v>25.34206718943006</v>
+        <v>25.34206718951126</v>
       </c>
       <c r="R5">
-        <v>-88.77958335032804</v>
+        <v>-88.77958335023982</v>
       </c>
       <c r="S5">
-        <v>155.097906710916</v>
+        <v>155.097906710987</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -949,55 +949,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>34.99498470490086</v>
+        <v>34.99498470490322</v>
       </c>
       <c r="D6">
-        <v>34.99498470490086</v>
+        <v>34.99498470490322</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.081745656291933</v>
+        <v>8.081745656292478</v>
       </c>
       <c r="G6">
-        <v>8.081745656291933</v>
+        <v>8.081745656292478</v>
       </c>
       <c r="H6">
-        <v>4155844.289106929</v>
+        <v>4155844.278728753</v>
       </c>
       <c r="I6">
-        <v>-0.1762120603730304</v>
+        <v>0.1558883839518523</v>
       </c>
       <c r="J6">
-        <v>0.0007617442565877214</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="K6">
-        <v>0.006240294732411511</v>
+        <v>0.006240294845061769</v>
       </c>
       <c r="L6">
-        <v>0.000761744441960696</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="M6">
-        <v>0.006240294610018257</v>
+        <v>0.006240294745720692</v>
       </c>
       <c r="N6">
-        <v>0.9526279698022332</v>
+        <v>0.9526279698015384</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279598150378</v>
+        <v>0.9526279598147934</v>
       </c>
       <c r="Q6">
-        <v>3.66411644169918E-08</v>
+        <v>3.66500825188063E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.999999963297</v>
+        <v>179.9999999633413</v>
       </c>
     </row>
   </sheetData>
@@ -1110,22 +1110,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049999952316283</v>
+        <v>1.050004138519517</v>
       </c>
       <c r="O2">
-        <v>1.049983921824037</v>
+        <v>1.049959518374843</v>
       </c>
       <c r="P2">
-        <v>1.049955331993708</v>
+        <v>1.04997554923967</v>
       </c>
       <c r="Q2">
-        <v>179.9999999999927</v>
+        <v>29.99859426342728</v>
       </c>
       <c r="R2">
-        <v>59.9976935400337</v>
+        <v>-90.00180143451601</v>
       </c>
       <c r="S2">
-        <v>-60.00039563978353</v>
+        <v>150.0005050713337</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1169,22 +1169,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049999952316282</v>
+        <v>1.050029087220757</v>
       </c>
       <c r="O3">
-        <v>1.049927663576831</v>
+        <v>1.049797089600012</v>
       </c>
       <c r="P3">
-        <v>1.049767948256762</v>
+        <v>1.049869387330141</v>
       </c>
       <c r="Q3">
-        <v>179.9999999999926</v>
+        <v>29.99269099044325</v>
       </c>
       <c r="R3">
-        <v>59.98765891417099</v>
+        <v>-90.01006399193564</v>
       </c>
       <c r="S3">
-        <v>-60.00275344354507</v>
+        <v>150.0022784719106</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1228,22 +1228,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049999952316282</v>
+        <v>1.050008313510062</v>
       </c>
       <c r="O4">
-        <v>1.049860334070212</v>
+        <v>1.049703970218123</v>
       </c>
       <c r="P4">
-        <v>1.049695606600151</v>
+        <v>1.049843609258966</v>
       </c>
       <c r="Q4">
-        <v>179.9999999999926</v>
+        <v>29.99041181059033</v>
       </c>
       <c r="R4">
-        <v>59.98522120795452</v>
+        <v>-90.01038004812526</v>
       </c>
       <c r="S4">
-        <v>-60.00078908506597</v>
+        <v>150.0044003598866</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1287,22 +1287,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.050008313510008</v>
+        <v>1.050008313510003</v>
       </c>
       <c r="O5">
-        <v>1.049703970218083</v>
+        <v>1.04970397021807</v>
       </c>
       <c r="P5">
-        <v>1.049843609259</v>
+        <v>1.049843609258998</v>
       </c>
       <c r="Q5">
-        <v>29.99041181059071</v>
+        <v>29.9904118105905</v>
       </c>
       <c r="R5">
-        <v>-90.01038004811977</v>
+        <v>-90.01038004811952</v>
       </c>
       <c r="S5">
-        <v>150.0044003598888</v>
+        <v>150.0044003598893</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1313,55 +1313,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.05931688229027837</v>
+        <v>0.05931688229204195</v>
       </c>
       <c r="D6">
-        <v>0.05931688229027837</v>
+        <v>0.05931688229204194</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.01369864738723837</v>
+        <v>0.01369864738764566</v>
       </c>
       <c r="G6">
-        <v>0.01369864738723837</v>
+        <v>0.01369864738764565</v>
       </c>
       <c r="H6">
-        <v>4155844.2130444</v>
+        <v>4155844.289159183</v>
       </c>
       <c r="I6">
-        <v>0.3382144411803715</v>
+        <v>-0.09667844596139809</v>
       </c>
       <c r="J6">
-        <v>0.000738532876650268</v>
+        <v>0.0007385327476024228</v>
       </c>
       <c r="K6">
-        <v>0.006009343808324313</v>
+        <v>0.006009344031841738</v>
       </c>
       <c r="L6">
-        <v>0.0007385329263208069</v>
+        <v>0.000738533019007294</v>
       </c>
       <c r="M6">
-        <v>0.006009343672621878</v>
+        <v>0.006009343634477428</v>
       </c>
       <c r="N6">
-        <v>1.050124249534636</v>
+        <v>1.050124249534613</v>
       </c>
       <c r="O6">
-        <v>1.048584227053803</v>
+        <v>1.048584227053728</v>
       </c>
       <c r="P6">
-        <v>1.049167932672657</v>
+        <v>1.049167932672642</v>
       </c>
       <c r="Q6">
-        <v>29.9514816404486</v>
+        <v>29.95148164044709</v>
       </c>
       <c r="R6">
-        <v>-90.06031761863325</v>
+        <v>-90.06031761863262</v>
       </c>
       <c r="S6">
-        <v>150.0184205536881</v>
+        <v>150.0184205536902</v>
       </c>
     </row>
   </sheetData>
@@ -1474,22 +1474,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100000023841856</v>
+        <v>1.100004408047329</v>
       </c>
       <c r="O2">
-        <v>1.099983229010163</v>
+        <v>1.099957665190902</v>
       </c>
       <c r="P2">
-        <v>1.09995328079912</v>
+        <v>1.099974460412913</v>
       </c>
       <c r="Q2">
-        <v>179.9999999999927</v>
+        <v>29.99859432538238</v>
       </c>
       <c r="R2">
-        <v>59.99769369346202</v>
+        <v>-90.00180125156575</v>
       </c>
       <c r="S2">
-        <v>-60.00039551879262</v>
+        <v>150.0005051008476</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1533,22 +1533,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.100000023841855</v>
+        <v>1.100030538759423</v>
       </c>
       <c r="O3">
-        <v>1.099924286805662</v>
+        <v>1.099787503773015</v>
       </c>
       <c r="P3">
-        <v>1.099756982111964</v>
+        <v>1.099863250228144</v>
       </c>
       <c r="Q3">
-        <v>179.9999999999926</v>
+        <v>29.99269129588961</v>
       </c>
       <c r="R3">
-        <v>59.98765970462204</v>
+        <v>-90.01006302180252</v>
       </c>
       <c r="S3">
-        <v>-60.00275277895614</v>
+        <v>150.0022786513711</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1592,22 +1592,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.100000023841855</v>
+        <v>1.100008775115286</v>
       </c>
       <c r="O4">
-        <v>1.099853752771306</v>
+        <v>1.099689954833212</v>
       </c>
       <c r="P4">
-        <v>1.099681201022607</v>
+        <v>1.099836247687823</v>
       </c>
       <c r="Q4">
-        <v>179.9999999999926</v>
+        <v>29.99041227879366</v>
       </c>
       <c r="R4">
-        <v>59.98522227455008</v>
+        <v>-90.01037885124788</v>
       </c>
       <c r="S4">
-        <v>-60.00078835665138</v>
+        <v>150.0044004898159</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1657,16 +1657,16 @@
         <v>1.099689954833153</v>
       </c>
       <c r="P5">
-        <v>1.099836247687857</v>
+        <v>1.099836247687858</v>
       </c>
       <c r="Q5">
-        <v>29.99041227879374</v>
+        <v>29.99041227879383</v>
       </c>
       <c r="R5">
-        <v>-90.01037885124195</v>
+        <v>-90.01037885124187</v>
       </c>
       <c r="S5">
-        <v>150.0044004898186</v>
+        <v>150.0044004898187</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1692,40 +1692,40 @@
         <v>0.01435023577937563</v>
       </c>
       <c r="H6">
-        <v>4155844.289106929</v>
+        <v>4155844.278728753</v>
       </c>
       <c r="I6">
-        <v>-0.1762120603730304</v>
+        <v>0.1558883839518523</v>
       </c>
       <c r="J6">
-        <v>0.0007617442565877214</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="K6">
-        <v>0.006240294732411511</v>
+        <v>0.006240294845061769</v>
       </c>
       <c r="L6">
-        <v>0.000761744441960696</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="M6">
-        <v>0.006240294610018257</v>
+        <v>0.006240294745720692</v>
       </c>
       <c r="N6">
-        <v>1.100135989306274</v>
+        <v>1.100135989306268</v>
       </c>
       <c r="O6">
-        <v>1.098461071904093</v>
+        <v>1.098461071904087</v>
       </c>
       <c r="P6">
-        <v>1.099094739754304</v>
+        <v>1.099094739754298</v>
       </c>
       <c r="Q6">
-        <v>29.94963030189226</v>
+        <v>29.94963030189233</v>
       </c>
       <c r="R6">
-        <v>-90.06269174365477</v>
+        <v>-90.06269174365468</v>
       </c>
       <c r="S6">
-        <v>150.0190896171581</v>
+        <v>150.0190896171582</v>
       </c>
     </row>
   </sheetData>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499999880799651</v>
+        <v>0.94330712213556</v>
       </c>
       <c r="O2">
-        <v>0.9284240862533489</v>
+        <v>0.9202096999460634</v>
       </c>
       <c r="P2">
-        <v>0.9270693299613975</v>
+        <v>0.9419737710209092</v>
       </c>
       <c r="Q2">
-        <v>-179.9999999999616</v>
+        <v>29.19323166864753</v>
       </c>
       <c r="R2">
-        <v>59.13315360072961</v>
+        <v>-90.0951201205981</v>
       </c>
       <c r="S2">
-        <v>-59.27352488998468</v>
+        <v>150.7614448423916</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1897,22 +1897,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499999880798641</v>
+        <v>0.9229023352358527</v>
       </c>
       <c r="O3">
-        <v>0.851927495338023</v>
+        <v>0.8065751367400146</v>
       </c>
       <c r="P3">
-        <v>0.8374453463809489</v>
+        <v>0.9095509723186813</v>
       </c>
       <c r="Q3">
-        <v>-179.9999999999652</v>
+        <v>25.9064631998193</v>
       </c>
       <c r="R3">
-        <v>55.06309862595015</v>
+        <v>-91.05627425268518</v>
       </c>
       <c r="S3">
-        <v>-56.5076936452158</v>
+        <v>153.684314908952</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1956,22 +1956,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.949999988079865</v>
+        <v>0.8892741171281174</v>
       </c>
       <c r="O4">
-        <v>0.7944503100017601</v>
+        <v>0.763665932646438</v>
       </c>
       <c r="P4">
-        <v>0.8335929334168654</v>
+        <v>0.9244102655068516</v>
       </c>
       <c r="Q4">
-        <v>-179.9999999999652</v>
+        <v>25.39291893518994</v>
       </c>
       <c r="R4">
-        <v>56.24244382761969</v>
+        <v>-87.09305248165519</v>
       </c>
       <c r="S4">
-        <v>-52.40631221192861</v>
+        <v>155.6364983177938</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2015,22 +2015,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.889274117103935</v>
+        <v>0.8892741171034219</v>
       </c>
       <c r="O5">
-        <v>0.7636659326704468</v>
+        <v>0.7636659326698279</v>
       </c>
       <c r="P5">
-        <v>0.9244102655408688</v>
+        <v>0.9244102655402699</v>
       </c>
       <c r="Q5">
-        <v>25.39291893669812</v>
+        <v>25.39291893666405</v>
       </c>
       <c r="R5">
-        <v>-87.09305247688548</v>
+        <v>-87.0930524769182</v>
       </c>
       <c r="S5">
-        <v>155.6364983180698</v>
+        <v>155.636498318046</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2041,55 +2041,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>29.83070076647896</v>
+        <v>29.83070076648736</v>
       </c>
       <c r="D6">
-        <v>29.83070076647896</v>
+        <v>29.83070076648736</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>6.88910534971239</v>
+        <v>6.889105349714329</v>
       </c>
       <c r="G6">
-        <v>6.88910534971239</v>
+        <v>6.889105349714329</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.8227241171668683</v>
+        <v>0.822724117167055</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8227241293776177</v>
+        <v>0.8227241293775091</v>
       </c>
       <c r="Q6">
-        <v>-6.462416434026289E-08</v>
+        <v>-6.464377389453028E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>-179.9999999353446</v>
+        <v>-179.9999999353503</v>
       </c>
     </row>
   </sheetData>
@@ -2202,22 +2202,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999999761589889</v>
+        <v>0.8936593664053256</v>
       </c>
       <c r="O2">
-        <v>0.8795596483977125</v>
+        <v>0.8717775983203651</v>
       </c>
       <c r="P2">
-        <v>0.87827619508639</v>
+        <v>0.8923961916827421</v>
       </c>
       <c r="Q2">
-        <v>-179.9999999999616</v>
+        <v>29.19323166864753</v>
       </c>
       <c r="R2">
-        <v>59.13315360072961</v>
+        <v>-90.0951201205981</v>
       </c>
       <c r="S2">
-        <v>-59.27352488998468</v>
+        <v>150.7614448423917</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2261,22 +2261,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999999761588934</v>
+        <v>0.874328515927757</v>
       </c>
       <c r="O3">
-        <v>0.807089194856778</v>
+        <v>0.7641238030998198</v>
       </c>
       <c r="P3">
-        <v>0.7933692644571574</v>
+        <v>0.861679856498371</v>
       </c>
       <c r="Q3">
-        <v>-179.9999999999652</v>
+        <v>25.9064631998193</v>
       </c>
       <c r="R3">
-        <v>55.06309862595014</v>
+        <v>-91.05627425268518</v>
       </c>
       <c r="S3">
-        <v>-56.50769364521579</v>
+        <v>153.684314908952</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2320,22 +2320,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999999761588942</v>
+        <v>0.8424702044804062</v>
       </c>
       <c r="O4">
-        <v>0.7526371252974172</v>
+        <v>0.7234729787358416</v>
       </c>
       <c r="P4">
-        <v>0.7897196101210169</v>
+        <v>0.8757570814277329</v>
       </c>
       <c r="Q4">
-        <v>-179.9999999999652</v>
+        <v>25.39291893518994</v>
       </c>
       <c r="R4">
-        <v>56.24244382761969</v>
+        <v>-87.09305248165519</v>
       </c>
       <c r="S4">
-        <v>-52.40631221192861</v>
+        <v>155.6364983177938</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2379,22 +2379,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8424702044574965</v>
+        <v>0.8424702044570104</v>
       </c>
       <c r="O5">
-        <v>0.7234729787585865</v>
+        <v>0.7234729787580003</v>
       </c>
       <c r="P5">
-        <v>0.8757570814599597</v>
+        <v>0.8757570814593924</v>
       </c>
       <c r="Q5">
-        <v>25.39291893669812</v>
+        <v>25.39291893666405</v>
       </c>
       <c r="R5">
-        <v>-87.09305247688548</v>
+        <v>-87.0930524769182</v>
       </c>
       <c r="S5">
-        <v>155.6364983180698</v>
+        <v>155.636498318046</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2405,55 +2405,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>28.26066349000537</v>
+        <v>28.26066349001332</v>
       </c>
       <c r="D6">
-        <v>28.26066349000537</v>
+        <v>28.26066349001332</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>6.526520766625549</v>
+        <v>6.526520766627384</v>
       </c>
       <c r="G6">
-        <v>6.526520766625549</v>
+        <v>6.526520766627384</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.7794228369751098</v>
+        <v>0.7794228369752865</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7794228485431881</v>
+        <v>0.779422848543085</v>
       </c>
       <c r="Q6">
-        <v>-6.462417781980791E-08</v>
+        <v>-6.464377864126903E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>-179.9999999353446</v>
+        <v>-179.9999999353503</v>
       </c>
     </row>
   </sheetData>
@@ -2566,22 +2566,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499999880790736</v>
+        <v>0.9500042913249493</v>
       </c>
       <c r="O2">
-        <v>0.9499835077079167</v>
+        <v>0.9499584202019964</v>
       </c>
       <c r="P2">
-        <v>0.9499541167483266</v>
+        <v>0.9499749010083767</v>
       </c>
       <c r="Q2">
-        <v>-179.9999999999926</v>
+        <v>29.99840273103076</v>
       </c>
       <c r="R2">
-        <v>59.99737929598987</v>
+        <v>-90.00204685423931</v>
       </c>
       <c r="S2">
-        <v>-60.00044951018038</v>
+        <v>150.0005739090119</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2625,22 +2625,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499999880790748</v>
+        <v>0.950027443029966</v>
       </c>
       <c r="O3">
-        <v>0.9499312985903238</v>
+        <v>0.9498076839092886</v>
       </c>
       <c r="P3">
-        <v>0.9497802226059008</v>
+        <v>0.9498763823371287</v>
       </c>
       <c r="Q3">
-        <v>-179.9999999999926</v>
+        <v>29.99234777609211</v>
       </c>
       <c r="R3">
-        <v>59.98708683730016</v>
+        <v>-90.01052169766035</v>
       </c>
       <c r="S3">
-        <v>-60.00286778612227</v>
+        <v>150.0023929725074</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2684,22 +2684,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499999880790748</v>
+        <v>0.9499838462230683</v>
       </c>
       <c r="O4">
-        <v>0.9498274465944929</v>
+        <v>0.9496871683818415</v>
       </c>
       <c r="P4">
-        <v>0.9497033152804033</v>
+        <v>0.949859735347882</v>
       </c>
       <c r="Q4">
-        <v>-179.9999999999926</v>
+        <v>29.98966943394186</v>
       </c>
       <c r="R4">
-        <v>59.98534566695211</v>
+        <v>-90.00864540853833</v>
       </c>
       <c r="S4">
-        <v>-59.99831164399074</v>
+        <v>150.0060099968998</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2743,22 +2743,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9499838462230094</v>
+        <v>0.9499838462230087</v>
       </c>
       <c r="O5">
-        <v>0.9496871683818029</v>
+        <v>0.9496871683818024</v>
       </c>
       <c r="P5">
-        <v>0.9498597353479225</v>
+        <v>0.9498597353479219</v>
       </c>
       <c r="Q5">
-        <v>29.98966943394271</v>
+        <v>29.98966943394257</v>
       </c>
       <c r="R5">
-        <v>-90.00864540853127</v>
+        <v>-90.00864540853141</v>
       </c>
       <c r="S5">
-        <v>150.0060099969027</v>
+        <v>150.0060099969025</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2769,10 +2769,10 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.05366222753997701</v>
+        <v>0.05366222753997704</v>
       </c>
       <c r="D6">
-        <v>0.05366222753997701</v>
+        <v>0.05366222753997704</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2784,40 +2784,40 @@
         <v>0.0123927607908748</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.9500940258818698</v>
+        <v>0.9500940258818683</v>
       </c>
       <c r="O6">
-        <v>0.948623110526039</v>
+        <v>0.9486231105260378</v>
       </c>
       <c r="P6">
-        <v>0.9492176836326831</v>
+        <v>0.9492176836326817</v>
       </c>
       <c r="Q6">
-        <v>29.94878109295409</v>
+        <v>29.94878109295402</v>
       </c>
       <c r="R6">
-        <v>-90.06109628202167</v>
+        <v>-90.06109628202177</v>
       </c>
       <c r="S6">
-        <v>150.0207371868657</v>
+        <v>150.0207371868656</v>
       </c>
     </row>
   </sheetData>
@@ -2930,22 +2930,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999999761581443</v>
+        <v>0.9000040529173383</v>
       </c>
       <c r="O2">
-        <v>0.899984363175161</v>
+        <v>0.8999605960646202</v>
       </c>
       <c r="P2">
-        <v>0.899956519108569</v>
+        <v>0.8999762094599209</v>
       </c>
       <c r="Q2">
-        <v>-179.9999999999926</v>
+        <v>29.99840273103075</v>
       </c>
       <c r="R2">
-        <v>59.99737929598987</v>
+        <v>-90.00204685423931</v>
       </c>
       <c r="S2">
-        <v>-60.00044951018038</v>
+        <v>150.0005739090119</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2989,22 +2989,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999999761581459</v>
+        <v>0.9000259861112587</v>
       </c>
       <c r="O3">
-        <v>0.8999349019065519</v>
+        <v>0.8998177932629936</v>
       </c>
       <c r="P3">
-        <v>0.8997917772917258</v>
+        <v>0.8998828759831977</v>
       </c>
       <c r="Q3">
-        <v>-179.9999999999926</v>
+        <v>29.99234777609211</v>
       </c>
       <c r="R3">
-        <v>59.98708683730016</v>
+        <v>-90.01052169766035</v>
       </c>
       <c r="S3">
-        <v>-60.00286778612227</v>
+        <v>150.0023929725074</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -3048,22 +3048,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999999761581459</v>
+        <v>0.899984683873721</v>
       </c>
       <c r="O4">
-        <v>0.8998365158066103</v>
+        <v>0.8997036206596356</v>
       </c>
       <c r="P4">
-        <v>0.8997189177212176</v>
+        <v>0.8998671051514998</v>
       </c>
       <c r="Q4">
-        <v>-179.9999999999926</v>
+        <v>29.98966943394186</v>
       </c>
       <c r="R4">
-        <v>59.9853456669521</v>
+        <v>-90.00864540853833</v>
       </c>
       <c r="S4">
-        <v>-59.99831164399074</v>
+        <v>150.0060099968998</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3107,22 +3107,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8999846838736651</v>
+        <v>0.8999846838736648</v>
       </c>
       <c r="O5">
-        <v>0.8997036206595989</v>
+        <v>0.8997036206595985</v>
       </c>
       <c r="P5">
-        <v>0.899867105151538</v>
+        <v>0.8998671051515376</v>
       </c>
       <c r="Q5">
-        <v>29.98966943394271</v>
+        <v>29.98966943394257</v>
       </c>
       <c r="R5">
-        <v>-90.00864540853127</v>
+        <v>-90.00864540853141</v>
       </c>
       <c r="S5">
-        <v>150.0060099969027</v>
+        <v>150.0060099969025</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3136,7 +3136,7 @@
         <v>0.05083789906590221</v>
       </c>
       <c r="D6">
-        <v>0.05083789906590221</v>
+        <v>0.05083789906590223</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -3148,40 +3148,40 @@
         <v>0.0117405100592407</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.9000890646016566</v>
+        <v>0.9000890646016553</v>
       </c>
       <c r="O6">
-        <v>0.8986955658629301</v>
+        <v>0.8986955658629289</v>
       </c>
       <c r="P6">
-        <v>0.8992588456403183</v>
+        <v>0.8992588456403169</v>
       </c>
       <c r="Q6">
-        <v>29.94878109295409</v>
+        <v>29.94878109295401</v>
       </c>
       <c r="R6">
-        <v>-90.06109628202167</v>
+        <v>-90.06109628202177</v>
       </c>
       <c r="S6">
-        <v>150.0207371868657</v>
+        <v>150.0207371868656</v>
       </c>
     </row>
   </sheetData>
@@ -3297,22 +3297,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049999952307435</v>
+        <v>1.049999952271328</v>
       </c>
       <c r="O2">
-        <v>1.049999952275753</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P2">
-        <v>1.049999952352391</v>
+        <v>1.049999952347966</v>
       </c>
       <c r="Q2">
-        <v>179.9999999951639</v>
+        <v>29.99999999658623</v>
       </c>
       <c r="R2">
-        <v>59.99999999899948</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00000000141385</v>
+        <v>149.9999999961632</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3359,22 +3359,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049999952294509</v>
+        <v>1.049999952097912</v>
       </c>
       <c r="O3">
-        <v>1.0499999521088</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P3">
-        <v>1.049999952512881</v>
+        <v>1.049999952501993</v>
       </c>
       <c r="Q3">
-        <v>179.999999974532</v>
+        <v>29.99999998141771</v>
       </c>
       <c r="R3">
-        <v>59.99999999414692</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S3">
-        <v>-60.00000000687726</v>
+        <v>149.9999999803838</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049999952189404</v>
+        <v>1.049999951967445</v>
       </c>
       <c r="O4">
-        <v>1.049999952030885</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P4">
-        <v>1.049999952538243</v>
+        <v>1.049999952474803</v>
       </c>
       <c r="Q4">
-        <v>179.9999999680246</v>
+        <v>29.99999997902064</v>
       </c>
       <c r="R4">
-        <v>59.99999999500354</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.00000001098755</v>
+        <v>149.9999999730198</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3527,40 +3527,40 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4155844.2130444</v>
+        <v>4155844.289159183</v>
       </c>
       <c r="I6">
-        <v>0.3382144411803715</v>
+        <v>-0.09667844596139809</v>
       </c>
       <c r="J6">
-        <v>0.000738532876650268</v>
+        <v>0.0007385327476024228</v>
       </c>
       <c r="K6">
-        <v>0.006009343808324313</v>
+        <v>0.006009344031841738</v>
       </c>
       <c r="L6">
-        <v>0.0007385329263208069</v>
+        <v>0.000738533019007294</v>
       </c>
       <c r="M6">
-        <v>0.006009343672621878</v>
+        <v>0.006009343634477428</v>
       </c>
       <c r="N6">
-        <v>1.049999950721423</v>
+        <v>1.049999950721532</v>
       </c>
       <c r="O6">
-        <v>1.049999952316226</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P6">
-        <v>1.049999953351244</v>
+        <v>1.049999953351251</v>
       </c>
       <c r="Q6">
-        <v>29.99999988454146</v>
+        <v>29.99999988454305</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999476</v>
+        <v>-89.99999999999794</v>
       </c>
       <c r="S6">
-        <v>149.9999998669009</v>
+        <v>149.9999998669024</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3679,22 +3679,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100000023832587</v>
+        <v>1.100000023794761</v>
       </c>
       <c r="O2">
-        <v>1.100000023799397</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="P2">
-        <v>1.100000023879684</v>
+        <v>1.100000023875048</v>
       </c>
       <c r="Q2">
-        <v>179.9999999951639</v>
+        <v>29.99999999658623</v>
       </c>
       <c r="R2">
-        <v>59.99999999899948</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00000000141385</v>
+        <v>149.9999999961632</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3741,22 +3741,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.100000023819046</v>
+        <v>1.100000023613087</v>
       </c>
       <c r="O3">
-        <v>1.100000023624493</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="P3">
-        <v>1.100000024047817</v>
+        <v>1.100000024036411</v>
       </c>
       <c r="Q3">
-        <v>179.999999974532</v>
+        <v>29.99999998141771</v>
       </c>
       <c r="R3">
-        <v>59.99999999414692</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00000000687726</v>
+        <v>149.9999999803838</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3803,22 +3803,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.100000023708936</v>
+        <v>1.100000023476407</v>
       </c>
       <c r="O4">
-        <v>1.100000023542868</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="P4">
-        <v>1.100000024074387</v>
+        <v>1.100000024007926</v>
       </c>
       <c r="Q4">
-        <v>179.9999999680246</v>
+        <v>29.99999997902066</v>
       </c>
       <c r="R4">
-        <v>59.99999999500353</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.00000001098755</v>
+        <v>149.9999999730198</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3874,10 +3874,10 @@
         <v>1.100000024007926</v>
       </c>
       <c r="Q5">
-        <v>29.99999997902065</v>
+        <v>29.99999997902066</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S5">
         <v>149.9999999730198</v>
@@ -3909,40 +3909,40 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4155844.289106929</v>
+        <v>4155844.278728753</v>
       </c>
       <c r="I6">
-        <v>-0.1762120603730304</v>
+        <v>0.1558883839518523</v>
       </c>
       <c r="J6">
-        <v>0.0007617442565877214</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="K6">
-        <v>0.006240294732411511</v>
+        <v>0.006240294845061769</v>
       </c>
       <c r="L6">
-        <v>0.000761744441960696</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="M6">
-        <v>0.006240294610018257</v>
+        <v>0.006240294745720692</v>
       </c>
       <c r="N6">
-        <v>1.100000022108896</v>
+        <v>1.100000022109009</v>
       </c>
       <c r="O6">
-        <v>1.100000023841797</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="P6">
-        <v>1.100000024969825</v>
+        <v>1.100000024969833</v>
       </c>
       <c r="Q6">
-        <v>29.99999988004249</v>
+        <v>29.99999988004409</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999476</v>
+        <v>-89.99999999999794</v>
       </c>
       <c r="S6">
-        <v>149.9999998618476</v>
+        <v>149.9999998618492</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4061,22 +4061,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049999952307435</v>
+        <v>1.049999952271328</v>
       </c>
       <c r="O2">
-        <v>1.049999952275753</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P2">
-        <v>1.049999952352391</v>
+        <v>1.049999952347966</v>
       </c>
       <c r="Q2">
-        <v>179.9999999951639</v>
+        <v>29.99999999658624</v>
       </c>
       <c r="R2">
-        <v>59.99999999899949</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00000000141385</v>
+        <v>149.9999999961632</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4123,22 +4123,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049999952294507</v>
+        <v>1.049999952097912</v>
       </c>
       <c r="O3">
-        <v>1.0499999521088</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P3">
-        <v>1.04999995251288</v>
+        <v>1.049999952501992</v>
       </c>
       <c r="Q3">
-        <v>179.999999974532</v>
+        <v>29.99999998141782</v>
       </c>
       <c r="R3">
-        <v>59.99999999414698</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S3">
-        <v>-60.00000000687726</v>
+        <v>149.9999999803838</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4185,22 +4185,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049999952189402</v>
+        <v>1.049999951967445</v>
       </c>
       <c r="O4">
-        <v>1.049999952030886</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P4">
-        <v>1.049999952538242</v>
+        <v>1.049999952474801</v>
       </c>
       <c r="Q4">
-        <v>179.9999999680247</v>
+        <v>29.99999997902079</v>
       </c>
       <c r="R4">
-        <v>59.99999999500362</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S4">
-        <v>-60.00000001098755</v>
+        <v>149.9999999730199</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>1.049999952474801</v>
       </c>
       <c r="Q5">
-        <v>29.9999999790208</v>
+        <v>29.99999997902079</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S5">
         <v>149.9999999730199</v>
@@ -4291,40 +4291,40 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4155844.2130444</v>
+        <v>4155844.289159183</v>
       </c>
       <c r="I6">
-        <v>0.3382144411803715</v>
+        <v>-0.09667844596139809</v>
       </c>
       <c r="J6">
-        <v>0.000738532876650268</v>
+        <v>0.0007385327476024228</v>
       </c>
       <c r="K6">
-        <v>0.006009343808324313</v>
+        <v>0.006009344031841738</v>
       </c>
       <c r="L6">
-        <v>0.0007385329263208069</v>
+        <v>0.000738533019007294</v>
       </c>
       <c r="M6">
-        <v>0.006009343672621878</v>
+        <v>0.006009343634477428</v>
       </c>
       <c r="N6">
-        <v>1.049999950721421</v>
+        <v>1.04999995072153</v>
       </c>
       <c r="O6">
-        <v>1.049999952316226</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="P6">
-        <v>1.049999953351231</v>
+        <v>1.049999953351239</v>
       </c>
       <c r="Q6">
-        <v>29.99999988454219</v>
+        <v>29.99999988454378</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999476</v>
+        <v>-89.99999999999795</v>
       </c>
       <c r="S6">
-        <v>149.9999998669011</v>
+        <v>149.9999998669027</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4380,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.069211965322743</v>
+        <v>1.069211965322762</v>
       </c>
       <c r="G2">
-        <v>149.9640291619602</v>
+        <v>-0.03597083799321057</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.9387871686716606</v>
+        <v>0.9387871686719225</v>
       </c>
       <c r="G3">
-        <v>149.2619585801569</v>
+        <v>-0.7380414197227492</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4426,10 +4426,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.8935122209062166</v>
+        <v>0.8935122209065726</v>
       </c>
       <c r="G4">
-        <v>151.2204167668212</v>
+        <v>1.22041676695381</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8935122209216565</v>
+        <v>0.8935122209219969</v>
       </c>
       <c r="G5">
-        <v>1.220416771394482</v>
+        <v>1.220416771520689</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4460,22 +4460,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>40.40872772417899</v>
+        <v>40.4087277242067</v>
       </c>
       <c r="C6">
-        <v>27.99598821217076</v>
+        <v>27.99598821218996</v>
       </c>
       <c r="D6">
-        <v>0.0007617443451978032</v>
+        <v>0.0007617443451851989</v>
       </c>
       <c r="E6">
-        <v>0.006240294707275744</v>
+        <v>0.006240294707272939</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>83.04041299938353</v>
+        <v>83.04041299949446</v>
       </c>
     </row>
   </sheetData>
@@ -4591,22 +4591,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100000023832587</v>
+        <v>1.100000023794761</v>
       </c>
       <c r="O2">
-        <v>1.100000023799397</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="P2">
-        <v>1.100000023879684</v>
+        <v>1.100000023875048</v>
       </c>
       <c r="Q2">
-        <v>179.9999999951639</v>
+        <v>29.99999999658625</v>
       </c>
       <c r="R2">
-        <v>59.99999999899949</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00000000141385</v>
+        <v>149.9999999961632</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4653,22 +4653,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.100000023819044</v>
+        <v>1.100000023613086</v>
       </c>
       <c r="O3">
-        <v>1.100000023624494</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="P3">
-        <v>1.100000024047815</v>
+        <v>1.100000024036409</v>
       </c>
       <c r="Q3">
-        <v>179.999999974532</v>
+        <v>29.99999998141783</v>
       </c>
       <c r="R3">
-        <v>59.99999999414698</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00000000687726</v>
+        <v>149.9999999803838</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4715,22 +4715,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.100000023708934</v>
+        <v>1.100000023476407</v>
       </c>
       <c r="O4">
-        <v>1.100000023542869</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="P4">
-        <v>1.100000024074385</v>
+        <v>1.100000024007923</v>
       </c>
       <c r="Q4">
-        <v>179.9999999680247</v>
+        <v>29.9999999790208</v>
       </c>
       <c r="R4">
-        <v>59.99999999500361</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.00000001098756</v>
+        <v>149.9999999730199</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4786,7 +4786,7 @@
         <v>1.100000024007923</v>
       </c>
       <c r="Q5">
-        <v>29.99999997902079</v>
+        <v>29.9999999790208</v>
       </c>
       <c r="R5">
         <v>-89.99999999999635</v>
@@ -4821,40 +4821,40 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4155844.289106929</v>
+        <v>4155844.278728753</v>
       </c>
       <c r="I6">
-        <v>-0.1762120603730304</v>
+        <v>0.1558883839518523</v>
       </c>
       <c r="J6">
-        <v>0.0007617442565877214</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="K6">
-        <v>0.006240294732411511</v>
+        <v>0.006240294845061769</v>
       </c>
       <c r="L6">
-        <v>0.000761744441960696</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="M6">
-        <v>0.006240294610018257</v>
+        <v>0.006240294745720692</v>
       </c>
       <c r="N6">
-        <v>1.100000022108894</v>
+        <v>1.100000022109007</v>
       </c>
       <c r="O6">
-        <v>1.100000023841797</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="P6">
-        <v>1.100000024969812</v>
+        <v>1.10000002496982</v>
       </c>
       <c r="Q6">
-        <v>29.99999988004324</v>
+        <v>29.99999988004485</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999477</v>
+        <v>-89.99999999999793</v>
       </c>
       <c r="S6">
-        <v>149.9999998618479</v>
+        <v>149.9999998618495</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4973,22 +4973,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499999880699729</v>
+        <v>0.9499999880328501</v>
       </c>
       <c r="O2">
-        <v>0.9499999880373994</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P2">
-        <v>0.9499999881161937</v>
+        <v>0.9499999881116443</v>
       </c>
       <c r="Q2">
-        <v>179.9999999945054</v>
+        <v>29.99999999612088</v>
       </c>
       <c r="R2">
-        <v>59.99999999886337</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00000000160698</v>
+        <v>149.9999999956408</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5035,22 +5035,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499999880579761</v>
+        <v>0.9499999878719023</v>
       </c>
       <c r="O3">
-        <v>0.9499999878824497</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P3">
-        <v>0.9499999882651451</v>
+        <v>0.9499999882545977</v>
       </c>
       <c r="Q3">
-        <v>179.9999999733412</v>
+        <v>29.99999998056106</v>
       </c>
       <c r="R3">
-        <v>59.99999999388563</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00000000721131</v>
+        <v>149.9999999794544</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5097,22 +5097,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499999878753936</v>
+        <v>0.9499999876882449</v>
       </c>
       <c r="O4">
-        <v>0.9499999877900834</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P4">
-        <v>0.94999998826622</v>
+        <v>0.9499999881643812</v>
       </c>
       <c r="Q4">
-        <v>179.9999999668339</v>
+        <v>29.99999998044878</v>
       </c>
       <c r="R4">
-        <v>59.99999999702704</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.0000000136064</v>
+        <v>149.9999999698056</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5203,40 +5203,40 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.9499999865040939</v>
+        <v>0.9499999865041926</v>
       </c>
       <c r="O6">
-        <v>0.9499999880790182</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P6">
-        <v>0.9499999889973069</v>
+        <v>0.9499999889973142</v>
       </c>
       <c r="Q6">
-        <v>29.99999988120926</v>
+        <v>29.99999988121084</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999476</v>
+        <v>-89.99999999999794</v>
       </c>
       <c r="S6">
-        <v>149.9999998583398</v>
+        <v>149.9999998583414</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5355,22 +5355,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999999761495225</v>
+        <v>0.899999976114354</v>
       </c>
       <c r="O2">
-        <v>0.8999999761186636</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P2">
-        <v>0.8999999761933107</v>
+        <v>0.8999999761890011</v>
       </c>
       <c r="Q2">
-        <v>179.9999999945054</v>
+        <v>29.99999999612088</v>
       </c>
       <c r="R2">
-        <v>59.99999999886337</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00000000160698</v>
+        <v>149.9999999956408</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999999761381573</v>
+        <v>0.8999999759618768</v>
       </c>
       <c r="O3">
-        <v>0.899999975971869</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P3">
-        <v>0.8999999763344227</v>
+        <v>0.8999999763244305</v>
       </c>
       <c r="Q3">
-        <v>179.9999999733412</v>
+        <v>29.99999998056106</v>
       </c>
       <c r="R3">
-        <v>59.99999999388563</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00000000721133</v>
+        <v>149.9999999794544</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5479,22 +5479,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999999759651846</v>
+        <v>0.8999999757878858</v>
       </c>
       <c r="O4">
-        <v>0.8999999758843644</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P4">
-        <v>0.8999999763354409</v>
+        <v>0.8999999762389624</v>
       </c>
       <c r="Q4">
-        <v>179.9999999668339</v>
+        <v>29.99999998044877</v>
       </c>
       <c r="R4">
-        <v>59.99999999702704</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.0000000136064</v>
+        <v>149.9999999698056</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5585,40 +5585,40 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.8999999746660585</v>
+        <v>0.8999999746661521</v>
       </c>
       <c r="O6">
-        <v>0.899999976158092</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P6">
-        <v>0.8999999770280497</v>
+        <v>0.8999999770280563</v>
       </c>
       <c r="Q6">
-        <v>29.99999988120926</v>
+        <v>29.99999988121084</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999476</v>
+        <v>-89.99999999999797</v>
       </c>
       <c r="S6">
-        <v>149.9999998583398</v>
+        <v>149.9999998583414</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5737,22 +5737,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499999880699723</v>
+        <v>0.9499999880328501</v>
       </c>
       <c r="O2">
-        <v>0.9499999880373995</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P2">
-        <v>0.9499999881161935</v>
+        <v>0.9499999881116441</v>
       </c>
       <c r="Q2">
-        <v>179.9999999945054</v>
+        <v>29.9999999961209</v>
       </c>
       <c r="R2">
-        <v>59.99999999886339</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00000000160698</v>
+        <v>149.9999999956408</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5799,22 +5799,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499999880579746</v>
+        <v>0.9499999878719017</v>
       </c>
       <c r="O3">
-        <v>0.9499999878824499</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P3">
-        <v>0.9499999882651441</v>
+        <v>0.9499999882545958</v>
       </c>
       <c r="Q3">
-        <v>179.9999999733413</v>
+        <v>29.99999998056117</v>
       </c>
       <c r="R3">
-        <v>59.99999999388569</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00000000721134</v>
+        <v>149.9999999794544</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5861,22 +5861,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499999878753925</v>
+        <v>0.9499999876882451</v>
       </c>
       <c r="O4">
-        <v>0.9499999877900844</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P4">
-        <v>0.9499999882662185</v>
+        <v>0.9499999881643792</v>
       </c>
       <c r="Q4">
-        <v>179.999999966834</v>
+        <v>29.99999998044894</v>
       </c>
       <c r="R4">
-        <v>59.99999999702712</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.0000000136064</v>
+        <v>149.9999999698057</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5932,7 +5932,7 @@
         <v>0.9499999881643792</v>
       </c>
       <c r="Q5">
-        <v>29.99999998044893</v>
+        <v>29.99999998044894</v>
       </c>
       <c r="R5">
         <v>-89.99999999999635</v>
@@ -5967,40 +5967,40 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.9499999865040926</v>
+        <v>0.9499999865041913</v>
       </c>
       <c r="O6">
-        <v>0.9499999880790182</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="P6">
-        <v>0.9499999889972953</v>
+        <v>0.9499999889973022</v>
       </c>
       <c r="Q6">
-        <v>29.99999988121003</v>
+        <v>29.99999988121161</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999474</v>
+        <v>-89.99999999999794</v>
       </c>
       <c r="S6">
-        <v>149.9999998583402</v>
+        <v>149.9999998583417</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6119,22 +6119,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999999761495223</v>
+        <v>0.8999999761143539</v>
       </c>
       <c r="O2">
-        <v>0.8999999761186638</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P2">
-        <v>0.8999999761933106</v>
+        <v>0.8999999761890007</v>
       </c>
       <c r="Q2">
-        <v>179.9999999945054</v>
+        <v>29.9999999961209</v>
       </c>
       <c r="R2">
-        <v>59.99999999886339</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>-60.00000000160698</v>
+        <v>149.9999999956408</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6181,22 +6181,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999999761381561</v>
+        <v>0.8999999759618764</v>
       </c>
       <c r="O3">
-        <v>0.8999999759718694</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P3">
-        <v>0.8999999763344216</v>
+        <v>0.8999999763244287</v>
       </c>
       <c r="Q3">
-        <v>179.9999999733413</v>
+        <v>29.99999998056117</v>
       </c>
       <c r="R3">
-        <v>59.99999999388569</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>-60.00000000721134</v>
+        <v>149.9999999794544</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6243,22 +6243,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999999759651834</v>
+        <v>0.899999975787886</v>
       </c>
       <c r="O4">
-        <v>0.8999999758843652</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P4">
-        <v>0.8999999763354396</v>
+        <v>0.8999999762389603</v>
       </c>
       <c r="Q4">
-        <v>179.999999966834</v>
+        <v>29.99999998044893</v>
       </c>
       <c r="R4">
-        <v>59.9999999970271</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>-60.0000000136064</v>
+        <v>149.9999999698057</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6349,40 +6349,40 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.8999999746660571</v>
+        <v>0.8999999746661506</v>
       </c>
       <c r="O6">
-        <v>0.899999976158092</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="P6">
-        <v>0.8999999770280384</v>
+        <v>0.8999999770280452</v>
       </c>
       <c r="Q6">
-        <v>29.99999988121003</v>
+        <v>29.99999988121161</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999477</v>
+        <v>-89.99999999999797</v>
       </c>
       <c r="S6">
-        <v>149.9999998583401</v>
+        <v>149.9999998583417</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6501,22 +6501,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049999952312956</v>
+        <v>1.042756082097416</v>
       </c>
       <c r="O2">
-        <v>1.027504579646199</v>
+        <v>1.019485521670978</v>
       </c>
       <c r="P2">
-        <v>1.026893559259701</v>
+        <v>1.042154003726708</v>
       </c>
       <c r="Q2">
-        <v>179.9999999987503</v>
+        <v>29.2644775259295</v>
       </c>
       <c r="R2">
-        <v>59.23431352317509</v>
+        <v>-90.03879109739097</v>
       </c>
       <c r="S2">
-        <v>-59.29162956043471</v>
+        <v>150.7169722363144</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6563,22 +6563,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.04999995230842</v>
+        <v>1.017850815590872</v>
       </c>
       <c r="O3">
-        <v>0.9386302705456672</v>
+        <v>0.8902319386899717</v>
       </c>
       <c r="P3">
-        <v>0.9268184945994136</v>
+        <v>1.006968728068343</v>
       </c>
       <c r="Q3">
-        <v>179.9999999935511</v>
+        <v>25.92977054135272</v>
       </c>
       <c r="R3">
-        <v>55.21460949722656</v>
+        <v>-90.7797968995725</v>
       </c>
       <c r="S3">
-        <v>-56.28012862128722</v>
+        <v>153.7687858186851</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6625,22 +6625,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049999952282144</v>
+        <v>0.9942448482935785</v>
       </c>
       <c r="O4">
-        <v>0.8913852176181791</v>
+        <v>0.8453339436598208</v>
       </c>
       <c r="P4">
-        <v>0.9102563145346595</v>
+        <v>1.011198185068273</v>
       </c>
       <c r="Q4">
-        <v>179.9999999919243</v>
+        <v>25.15127081230298</v>
       </c>
       <c r="R4">
-        <v>55.19339622195393</v>
+        <v>-88.73279948474018</v>
       </c>
       <c r="S4">
-        <v>-53.51967072468348</v>
+        <v>155.2989288375506</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6687,22 +6687,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.99424484805388</v>
+        <v>0.9942448482657282</v>
       </c>
       <c r="O5">
-        <v>0.8453339436692756</v>
+        <v>0.8453339436744137</v>
       </c>
       <c r="P5">
-        <v>1.011198185306323</v>
+        <v>1.011198185101756</v>
       </c>
       <c r="Q5">
-        <v>25.15127081864265</v>
+        <v>25.15127081347351</v>
       </c>
       <c r="R5">
-        <v>-88.73279944911445</v>
+        <v>-88.7327994801733</v>
       </c>
       <c r="S5">
-        <v>155.2989288437472</v>
+        <v>155.2989288380147</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6716,55 +6716,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>34.68462523841514</v>
+        <v>34.6846252289839</v>
       </c>
       <c r="D6">
-        <v>34.68462515154603</v>
+        <v>34.6846251421148</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.010071206615468</v>
+        <v>8.010071204437418</v>
       </c>
       <c r="G6">
-        <v>8.010071186553906</v>
+        <v>8.010071184375859</v>
       </c>
       <c r="H6">
-        <v>4155844.2130444</v>
+        <v>4155844.289159183</v>
       </c>
       <c r="I6">
-        <v>0.3382144411803715</v>
+        <v>-0.09667844596139809</v>
       </c>
       <c r="J6">
-        <v>0.000738532876650268</v>
+        <v>0.0007385327476024228</v>
       </c>
       <c r="K6">
-        <v>0.006009343808324313</v>
+        <v>0.006009344031841738</v>
       </c>
       <c r="L6">
-        <v>0.0007385329263208069</v>
+        <v>0.000738533019007294</v>
       </c>
       <c r="M6">
-        <v>0.006009343672621878</v>
+        <v>0.006009343634477428</v>
       </c>
       <c r="N6">
-        <v>0.9093266318046653</v>
+        <v>0.9093266329685805</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9093266333862773</v>
+        <v>0.909326632223222</v>
       </c>
       <c r="Q6">
-        <v>-4.763378318111965E-08</v>
+        <v>-3.854378213102334E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999646164</v>
+        <v>179.9999999556839</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6883,22 +6883,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100000023838414</v>
+        <v>1.092677014726657</v>
       </c>
       <c r="O2">
-        <v>1.077288329885041</v>
+        <v>1.069211965333771</v>
       </c>
       <c r="P2">
-        <v>1.076694580992592</v>
+        <v>1.092091632401728</v>
       </c>
       <c r="Q2">
-        <v>179.9999999987516</v>
+        <v>29.29211872134177</v>
       </c>
       <c r="R2">
-        <v>59.26415433989509</v>
+        <v>-90.03597084195322</v>
       </c>
       <c r="S2">
-        <v>-59.31733392689746</v>
+        <v>150.6906508024699</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6945,22 +6945,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.100000023833712</v>
+        <v>1.067403370101402</v>
       </c>
       <c r="O3">
-        <v>0.9874262516527776</v>
+        <v>0.9387871687546696</v>
       </c>
       <c r="P3">
-        <v>0.9756902408640977</v>
+        <v>1.056556102750825</v>
       </c>
       <c r="Q3">
-        <v>179.9999999935539</v>
+        <v>26.0857802799717</v>
       </c>
       <c r="R3">
-        <v>55.41631507606557</v>
+        <v>-90.73804144315235</v>
       </c>
       <c r="S3">
-        <v>-56.42897644119873</v>
+        <v>153.6258712055936</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7007,22 +7007,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.100000023806186</v>
+        <v>1.043533396949182</v>
       </c>
       <c r="O4">
-        <v>0.9397573989486888</v>
+        <v>0.8935122209121119</v>
       </c>
       <c r="P4">
-        <v>0.958854624375115</v>
+        <v>1.060763957002285</v>
       </c>
       <c r="Q4">
-        <v>179.9999999919271</v>
+        <v>25.342067197768</v>
       </c>
       <c r="R4">
-        <v>55.40861807587861</v>
+        <v>-88.77958326534905</v>
       </c>
       <c r="S4">
-        <v>-53.7869629463757</v>
+        <v>155.0979067202207</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7069,22 +7069,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.043533396947683</v>
+        <v>1.043533396919833</v>
       </c>
       <c r="O5">
-        <v>0.8935122209270114</v>
+        <v>0.8935122209275363</v>
       </c>
       <c r="P5">
-        <v>1.06076395700844</v>
+        <v>1.060763957037653</v>
       </c>
       <c r="Q5">
-        <v>25.34206719818087</v>
+        <v>25.3420671989535</v>
       </c>
       <c r="R5">
-        <v>-88.77958326489662</v>
+        <v>-88.77958326078218</v>
       </c>
       <c r="S5">
-        <v>155.0979067198635</v>
+        <v>155.0979067206936</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7098,55 +7098,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>34.99498477762713</v>
+        <v>34.99498477891139</v>
       </c>
       <c r="D6">
-        <v>34.99498468661227</v>
+        <v>34.99498468789655</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.081745673087346</v>
+        <v>8.081745673383931</v>
       </c>
       <c r="G6">
-        <v>8.081745652068363</v>
+        <v>8.081745652364956</v>
       </c>
       <c r="H6">
-        <v>4155844.289106929</v>
+        <v>4155844.278728753</v>
       </c>
       <c r="I6">
-        <v>-0.1762120603730304</v>
+        <v>0.1558883839518523</v>
       </c>
       <c r="J6">
-        <v>0.0007617442565877214</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="K6">
-        <v>0.006240294732411511</v>
+        <v>0.006240294845061769</v>
       </c>
       <c r="L6">
-        <v>0.000761744441960696</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="M6">
-        <v>0.006240294610018257</v>
+        <v>0.006240294745720692</v>
       </c>
       <c r="N6">
-        <v>0.9526279662106086</v>
+        <v>0.9526279660447174</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279632321035</v>
+        <v>0.952627963397003</v>
       </c>
       <c r="Q6">
-        <v>-3.210314174224104E-08</v>
+        <v>-3.330845371343436E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999460092</v>
+        <v>179.9999999472646</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7265,22 +7265,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049999952314071</v>
+        <v>1.050002053519732</v>
       </c>
       <c r="O2">
-        <v>1.049991942564423</v>
+        <v>1.04997973026562</v>
       </c>
       <c r="P2">
-        <v>1.049977629015286</v>
+        <v>1.049987740108429</v>
       </c>
       <c r="Q2">
-        <v>179.9999999987855</v>
+        <v>29.99929671541621</v>
       </c>
       <c r="R2">
-        <v>59.99884577036807</v>
+        <v>-90.00090188824248</v>
       </c>
       <c r="S2">
-        <v>-60.00019859031348</v>
+        <v>150.0002523516698</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7327,22 +7327,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049999952310839</v>
+        <v>1.050014562658118</v>
       </c>
       <c r="O3">
-        <v>1.04996383694283</v>
+        <v>1.049898497017661</v>
       </c>
       <c r="P3">
-        <v>1.049883885055196</v>
+        <v>1.049934614633216</v>
       </c>
       <c r="Q3">
-        <v>179.9999999936275</v>
+        <v>29.99634339291988</v>
       </c>
       <c r="R3">
-        <v>59.99382446713084</v>
+        <v>-90.00503781811662</v>
       </c>
       <c r="S3">
-        <v>-60.00138083238294</v>
+        <v>150.0011380535503</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7389,22 +7389,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049999952284563</v>
+        <v>1.05000417821581</v>
       </c>
       <c r="O4">
-        <v>1.049930158571341</v>
+        <v>1.049851907180981</v>
       </c>
       <c r="P4">
-        <v>1.049847680636801</v>
+        <v>1.049921706095978</v>
       </c>
       <c r="Q4">
-        <v>179.9999999920007</v>
+        <v>29.99520276689578</v>
       </c>
       <c r="R4">
-        <v>59.99260410384566</v>
+        <v>-90.00519704499432</v>
       </c>
       <c r="S4">
-        <v>-60.00039912569802</v>
+        <v>150.0021992481838</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7451,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.050004178215781</v>
+        <v>1.05000417821578</v>
       </c>
       <c r="O5">
-        <v>1.049851907180956</v>
+        <v>1.049851907180954</v>
       </c>
       <c r="P5">
         <v>1.049921706095994</v>
       </c>
       <c r="Q5">
-        <v>29.99520276689586</v>
+        <v>29.99520276689587</v>
       </c>
       <c r="R5">
-        <v>-90.00519704499152</v>
+        <v>-90.00519704499146</v>
       </c>
       <c r="S5">
-        <v>150.002199248185</v>
+        <v>150.0021992481851</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7480,55 +7480,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.0296784840896378</v>
+        <v>0.02967848408986539</v>
       </c>
       <c r="D6">
-        <v>0.02967842216939036</v>
+        <v>0.02967842216961265</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.006853952413448811</v>
+        <v>0.006853952413501373</v>
       </c>
       <c r="G6">
-        <v>0.006853938113579989</v>
+        <v>0.006853938113631323</v>
       </c>
       <c r="H6">
-        <v>4155844.2130444</v>
+        <v>4155844.289159183</v>
       </c>
       <c r="I6">
-        <v>0.3382144411803715</v>
+        <v>-0.09667844596139809</v>
       </c>
       <c r="J6">
-        <v>0.000738532876650268</v>
+        <v>0.0007385327476024228</v>
       </c>
       <c r="K6">
-        <v>0.006009343808324313</v>
+        <v>0.006009344031841738</v>
       </c>
       <c r="L6">
-        <v>0.0007385329263208069</v>
+        <v>0.000738533019007294</v>
       </c>
       <c r="M6">
-        <v>0.006009343672621878</v>
+        <v>0.006009343634477428</v>
       </c>
       <c r="N6">
-        <v>1.050062282354662</v>
+        <v>1.050062282354605</v>
       </c>
       <c r="O6">
-        <v>1.049291757515471</v>
+        <v>1.049291757515433</v>
       </c>
       <c r="P6">
-        <v>1.049583559738607</v>
+        <v>1.049583559738601</v>
       </c>
       <c r="Q6">
-        <v>29.97572477504518</v>
+        <v>29.97572477504425</v>
       </c>
       <c r="R6">
-        <v>-90.0301791547429</v>
+        <v>-90.03017915474116</v>
       </c>
       <c r="S6">
-        <v>150.0092008526902</v>
+        <v>150.0092008526897</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7647,22 +7647,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.100000023839539</v>
+        <v>1.100002224766717</v>
       </c>
       <c r="O2">
-        <v>1.099991632426178</v>
+        <v>1.099978839014074</v>
       </c>
       <c r="P2">
-        <v>1.099976638040105</v>
+        <v>1.099987230525031</v>
       </c>
       <c r="Q2">
-        <v>179.9999999987855</v>
+        <v>29.99929673090777</v>
       </c>
       <c r="R2">
-        <v>59.99884580876412</v>
+        <v>-90.00090184243298</v>
       </c>
       <c r="S2">
-        <v>-60.00019855999609</v>
+        <v>150.0002523590822</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7709,22 +7709,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.100000023836153</v>
+        <v>1.100015328069929</v>
       </c>
       <c r="O3">
-        <v>1.099962187187776</v>
+        <v>1.099893738025532</v>
       </c>
       <c r="P3">
-        <v>1.099878432099897</v>
+        <v>1.099931577028501</v>
       </c>
       <c r="Q3">
-        <v>179.9999999936275</v>
+        <v>29.9963434692906</v>
       </c>
       <c r="R3">
-        <v>59.99382466493341</v>
+        <v>-90.00503757523742</v>
       </c>
       <c r="S3">
-        <v>-60.00138066588674</v>
+        <v>150.0011380985992</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7771,22 +7771,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.100000023808626</v>
+        <v>1.100004448951734</v>
       </c>
       <c r="O4">
-        <v>1.099926905492332</v>
+        <v>1.099844930798714</v>
       </c>
       <c r="P4">
-        <v>1.099840505013796</v>
+        <v>1.099918054564372</v>
       </c>
       <c r="Q4">
-        <v>179.9999999920007</v>
+        <v>29.99520288400387</v>
       </c>
       <c r="R4">
-        <v>59.99260437079025</v>
+        <v>-90.00519674530969</v>
       </c>
       <c r="S4">
-        <v>-60.000398943154</v>
+        <v>150.0021992808797</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7836,19 +7836,19 @@
         <v>1.100004448951702</v>
       </c>
       <c r="O5">
-        <v>1.099844930798687</v>
+        <v>1.099844930798684</v>
       </c>
       <c r="P5">
         <v>1.09991805456439</v>
       </c>
       <c r="Q5">
-        <v>29.99520288400397</v>
+        <v>29.99520288400396</v>
       </c>
       <c r="R5">
-        <v>-90.00519674530678</v>
+        <v>-90.00519674530669</v>
       </c>
       <c r="S5">
-        <v>150.002199280881</v>
+        <v>150.0021992808811</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7862,55 +7862,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.03109095729532975</v>
+        <v>0.03109095729565417</v>
       </c>
       <c r="D6">
-        <v>0.03109089242514358</v>
+        <v>0.03109089242547301</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.007180149132521275</v>
+        <v>0.007180149132596196</v>
       </c>
       <c r="G6">
-        <v>0.007180134151393272</v>
+        <v>0.007180134151469351</v>
       </c>
       <c r="H6">
-        <v>4155844.289106929</v>
+        <v>4155844.278728753</v>
       </c>
       <c r="I6">
-        <v>-0.1762120603730304</v>
+        <v>0.1558883839518523</v>
       </c>
       <c r="J6">
-        <v>0.0007617442565877214</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="K6">
-        <v>0.006240294732411511</v>
+        <v>0.006240294845061769</v>
       </c>
       <c r="L6">
-        <v>0.000761744441960696</v>
+        <v>0.0007617444419606958</v>
       </c>
       <c r="M6">
-        <v>0.006240294610018257</v>
+        <v>0.006240294745720692</v>
       </c>
       <c r="N6">
-        <v>1.100068211998498</v>
+        <v>1.100068211998434</v>
       </c>
       <c r="O6">
-        <v>1.099230173732632</v>
+        <v>1.099230173732584</v>
       </c>
       <c r="P6">
-        <v>1.099546949756177</v>
+        <v>1.099546949756167</v>
       </c>
       <c r="Q6">
-        <v>29.97479787196113</v>
+        <v>29.97479787196007</v>
       </c>
       <c r="R6">
-        <v>-90.03136781435472</v>
+        <v>-90.03136781435302</v>
       </c>
       <c r="S6">
-        <v>150.0095346223737</v>
+        <v>150.0095346223733</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8029,22 +8029,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499999880776905</v>
+        <v>0.9433071219299074</v>
       </c>
       <c r="O2">
-        <v>0.9284240863865162</v>
+        <v>0.9202096998635362</v>
       </c>
       <c r="P2">
-        <v>0.9270693299008569</v>
+        <v>0.9419737711831019</v>
       </c>
       <c r="Q2">
-        <v>179.999999998652</v>
+        <v>29.1932316714082</v>
       </c>
       <c r="R2">
-        <v>59.13315359074696</v>
+        <v>-90.0951200957347</v>
       </c>
       <c r="S2">
-        <v>-59.27352490281893</v>
+        <v>150.7614448493941</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8091,22 +8091,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499999880745904</v>
+        <v>0.9229023342227897</v>
       </c>
       <c r="O3">
-        <v>0.8519274960734831</v>
+        <v>0.8065751362089574</v>
       </c>
       <c r="P3">
-        <v>0.8374453460917497</v>
+        <v>0.9095509731028862</v>
       </c>
       <c r="Q3">
-        <v>179.9999999933573</v>
+        <v>25.90646320664975</v>
       </c>
       <c r="R3">
-        <v>55.06309857902851</v>
+        <v>-91.0562741177131</v>
       </c>
       <c r="S3">
-        <v>-56.50769371403082</v>
+        <v>153.6843149440866</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8153,22 +8153,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499999880289456</v>
+        <v>0.8892741158875683</v>
       </c>
       <c r="O4">
-        <v>0.7944503106270223</v>
+        <v>0.7636659329171264</v>
       </c>
       <c r="P4">
-        <v>0.8335929325679625</v>
+        <v>0.9244102667335643</v>
       </c>
       <c r="Q4">
-        <v>179.9999999917305</v>
+        <v>25.39291896957836</v>
       </c>
       <c r="R4">
-        <v>56.24244374186049</v>
+        <v>-87.09305228654114</v>
       </c>
       <c r="S4">
-        <v>-52.4063122873204</v>
+        <v>155.6364983394161</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8215,22 +8215,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8892741177053139</v>
+        <v>0.8892741158628727</v>
       </c>
       <c r="O5">
-        <v>0.7636659325074495</v>
+        <v>0.7636659329405161</v>
       </c>
       <c r="P5">
-        <v>0.9244102648165277</v>
+        <v>0.9244102667669826</v>
       </c>
       <c r="Q5">
-        <v>25.39291890684304</v>
+        <v>25.39291897105248</v>
       </c>
       <c r="R5">
-        <v>-87.0930525943716</v>
+        <v>-87.09305228180415</v>
       </c>
       <c r="S5">
-        <v>155.6364982924761</v>
+        <v>155.6364983396683</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8244,55 +8244,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>29.83070076871249</v>
+        <v>29.83070086693032</v>
       </c>
       <c r="D6">
-        <v>29.83070069042521</v>
+        <v>29.83070078864302</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>6.8891053502282</v>
+        <v>6.889105372910638</v>
       </c>
       <c r="G6">
-        <v>6.889105332148529</v>
+        <v>6.889105354830962</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.8227241209373161</v>
+        <v>0.822724110653187</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8227241254176615</v>
+        <v>0.8227241357018226</v>
       </c>
       <c r="Q6">
-        <v>-6.709924915349745E-08</v>
+        <v>-1.760273587796734E-07</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999803035</v>
+        <v>-179.9999999107824</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         <v>1.049979730265621</v>
       </c>
       <c r="G2">
-        <v>149.9990981117478</v>
+        <v>-0.000901888246122816</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8371,10 +8371,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1.049898497017662</v>
+        <v>1.049898497017663</v>
       </c>
       <c r="G3">
-        <v>149.9949621818736</v>
+        <v>-0.005037818120266383</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8394,10 +8394,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1.049851907180982</v>
+        <v>1.049851907180983</v>
       </c>
       <c r="G4">
-        <v>149.9948029549959</v>
+        <v>-0.005197044997986881</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8417,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1.049851907180955</v>
+        <v>1.049851907180956</v>
       </c>
       <c r="G5">
-        <v>-0.005197044995163723</v>
+        <v>-0.005197044995118756</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8428,22 +8428,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03426972580693886</v>
+        <v>0.03426972580693888</v>
       </c>
       <c r="C6">
-        <v>0.02374276285742371</v>
+        <v>0.02374276285742373</v>
       </c>
       <c r="D6">
-        <v>0.0007385329100661764</v>
+        <v>0.0007385329100534611</v>
       </c>
       <c r="E6">
-        <v>0.00600934383484958</v>
+        <v>0.006009343834854926</v>
       </c>
       <c r="F6">
         <v>1.049291757515442</v>
       </c>
       <c r="G6">
-        <v>44.99999999999815</v>
+        <v>44.99999999999827</v>
       </c>
     </row>
   </sheetData>
@@ -8559,22 +8559,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999999761568341</v>
+        <v>0.8936593662104968</v>
       </c>
       <c r="O2">
-        <v>0.8795596485238709</v>
+        <v>0.8717775982421817</v>
       </c>
       <c r="P2">
-        <v>0.8782761950290358</v>
+        <v>0.8923961918363983</v>
       </c>
       <c r="Q2">
-        <v>179.999999998652</v>
+        <v>29.1932316714082</v>
       </c>
       <c r="R2">
-        <v>59.13315359074696</v>
+        <v>-90.0951200957347</v>
       </c>
       <c r="S2">
-        <v>-59.27352490281893</v>
+        <v>150.7614448493941</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8621,22 +8621,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999999761538972</v>
+        <v>0.8743285149680131</v>
       </c>
       <c r="O3">
-        <v>0.8070891955535298</v>
+        <v>0.7641238025967131</v>
       </c>
       <c r="P3">
-        <v>0.7933692641831792</v>
+        <v>0.8616798572413021</v>
       </c>
       <c r="Q3">
-        <v>179.9999999933573</v>
+        <v>25.90646320664975</v>
       </c>
       <c r="R3">
-        <v>55.06309857902851</v>
+        <v>-91.0562741177131</v>
       </c>
       <c r="S3">
-        <v>-56.50769371403082</v>
+        <v>153.6843149440866</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8683,22 +8683,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999999761106549</v>
+        <v>0.8424702033051493</v>
       </c>
       <c r="O4">
-        <v>0.7526371258897709</v>
+        <v>0.723472978992283</v>
       </c>
       <c r="P4">
-        <v>0.7897196093167929</v>
+        <v>0.8757570825898817</v>
       </c>
       <c r="Q4">
-        <v>179.9999999917305</v>
+        <v>25.39291896957836</v>
       </c>
       <c r="R4">
-        <v>56.24244374186048</v>
+        <v>-87.09305228654114</v>
       </c>
       <c r="S4">
-        <v>-52.4063122873204</v>
+        <v>155.6364983394161</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8745,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.842470205027224</v>
+        <v>0.8424702032817534</v>
       </c>
       <c r="O5">
-        <v>0.7234729786041683</v>
+        <v>0.7234729790144417</v>
       </c>
       <c r="P5">
-        <v>0.8757570807737416</v>
+        <v>0.8757570826215409</v>
       </c>
       <c r="Q5">
-        <v>25.39291890684304</v>
+        <v>25.39291897105247</v>
       </c>
       <c r="R5">
-        <v>-87.0930525943716</v>
+        <v>-87.09305228180415</v>
       </c>
       <c r="S5">
-        <v>155.6364982924761</v>
+        <v>155.6364983396683</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8774,55 +8774,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>28.26066349212133</v>
+        <v>28.26066358516982</v>
       </c>
       <c r="D6">
-        <v>28.26066341795445</v>
+        <v>28.2606635110029</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>6.526520767114209</v>
+        <v>6.526520788602836</v>
       </c>
       <c r="G6">
-        <v>6.5265207499861</v>
+        <v>6.52652077147472</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.7794228405471126</v>
+        <v>0.7794228308042538</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7794228447916505</v>
+        <v>0.7794228545345399</v>
       </c>
       <c r="Q6">
-        <v>-6.709925036341549E-08</v>
+        <v>-1.76027368303631E-07</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999803035</v>
+        <v>-179.9999999107824</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8941,22 +8941,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9499999880767976</v>
+        <v>0.9500021482186386</v>
       </c>
       <c r="O2">
-        <v>0.9499917532425652</v>
+        <v>0.9499791979636321</v>
       </c>
       <c r="P2">
-        <v>0.9499770377696043</v>
+        <v>0.9499874329066977</v>
       </c>
       <c r="Q2">
-        <v>179.999999998621</v>
+        <v>29.99920085275554</v>
       </c>
       <c r="R2">
-        <v>59.99868844383818</v>
+        <v>-90.00102481525582</v>
       </c>
       <c r="S2">
-        <v>-60.00022565059228</v>
+        <v>150.0002867543702</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -9003,22 +9003,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.949999988073799</v>
+        <v>0.9500137571638075</v>
       </c>
       <c r="O3">
-        <v>0.949965669422647</v>
+        <v>0.9499038087630121</v>
       </c>
       <c r="P3">
-        <v>0.9498900380792483</v>
+        <v>0.9499381296490164</v>
       </c>
       <c r="Q3">
-        <v>179.9999999933299</v>
+        <v>29.99617149462365</v>
       </c>
       <c r="R3">
-        <v>59.99353786382203</v>
+        <v>-90.00526722363973</v>
       </c>
       <c r="S3">
-        <v>-60.00143830263816</v>
+        <v>150.0011952835038</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9065,22 +9065,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499999880281536</v>
+        <v>0.9499919530017827</v>
       </c>
       <c r="O4">
-        <v>0.9499137117015271</v>
+        <v>0.9498435003064288</v>
       </c>
       <c r="P4">
-        <v>0.9498515365885946</v>
+        <v>0.9499297830099235</v>
       </c>
       <c r="Q4">
-        <v>179.9999999917031</v>
+        <v>29.99483075058162</v>
       </c>
       <c r="R4">
-        <v>59.99266541016662</v>
+        <v>-90.00433015760095</v>
       </c>
       <c r="S4">
-        <v>-59.99916011567358</v>
+        <v>150.0030046931367</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9499919530017511</v>
+        <v>0.9499919530017529</v>
       </c>
       <c r="O5">
-        <v>0.9498435003064045</v>
+        <v>0.9498435003064094</v>
       </c>
       <c r="P5">
-        <v>0.9499297830099434</v>
+        <v>0.9499297830099436</v>
       </c>
       <c r="Q5">
-        <v>29.99483075058194</v>
+        <v>29.99483075058197</v>
       </c>
       <c r="R5">
-        <v>-90.00433015759731</v>
+        <v>-90.00433015759749</v>
       </c>
       <c r="S5">
-        <v>150.0030046931383</v>
+        <v>150.0030046931381</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9156,55 +9156,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.02685060346661445</v>
+        <v>0.02685060346601632</v>
       </c>
       <c r="D6">
-        <v>0.02685054744314138</v>
+        <v>0.02685054744254405</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.006200881348141832</v>
+        <v>0.006200881348003701</v>
       </c>
       <c r="G6">
-        <v>0.006200868410074735</v>
+        <v>0.006200868409936789</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.9500471721884678</v>
+        <v>0.9500471721884265</v>
       </c>
       <c r="O6">
-        <v>0.9493111849763758</v>
+        <v>0.9493111849763756</v>
       </c>
       <c r="P6">
-        <v>0.9496084452503833</v>
+        <v>0.9496084452503841</v>
       </c>
       <c r="Q6">
-        <v>29.97437218926657</v>
+        <v>29.97437218926636</v>
       </c>
       <c r="R6">
-        <v>-90.03057029446065</v>
+        <v>-90.03057029445934</v>
       </c>
       <c r="S6">
-        <v>150.0103592233241</v>
+        <v>150.0103592233225</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9323,22 +9323,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999999761559883</v>
+        <v>0.9000020226061251</v>
       </c>
       <c r="O2">
-        <v>0.8999921747341927</v>
+        <v>0.8999802802595798</v>
       </c>
       <c r="P2">
-        <v>0.8999782337600032</v>
+        <v>0.8999880817844805</v>
       </c>
       <c r="Q2">
-        <v>179.999999998621</v>
+        <v>29.99920085275553</v>
       </c>
       <c r="R2">
-        <v>59.99868844383818</v>
+        <v>-90.00102481525582</v>
       </c>
       <c r="S2">
-        <v>-60.0002256505923</v>
+        <v>150.0002867543703</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -9385,22 +9385,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999999761531475</v>
+        <v>0.9000130205540262</v>
       </c>
       <c r="O3">
-        <v>0.8999674637472463</v>
+        <v>0.8999088589126196</v>
       </c>
       <c r="P3">
-        <v>0.8998958130018675</v>
+        <v>0.8999413734357495</v>
       </c>
       <c r="Q3">
-        <v>179.9999999933299</v>
+        <v>29.99617149462365</v>
       </c>
       <c r="R3">
-        <v>59.99353786382202</v>
+        <v>-90.00526722363973</v>
       </c>
       <c r="S3">
-        <v>-60.00143830263816</v>
+        <v>150.0011952835038</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9447,22 +9447,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999999761099043</v>
+        <v>0.8999923639797645</v>
       </c>
       <c r="O4">
-        <v>0.8999182406437136</v>
+        <v>0.8998517245861271</v>
       </c>
       <c r="P4">
-        <v>0.8998593379059674</v>
+        <v>0.8999334660935613</v>
       </c>
       <c r="Q4">
-        <v>179.9999999917031</v>
+        <v>29.99483075058162</v>
       </c>
       <c r="R4">
-        <v>59.99266541016662</v>
+        <v>-90.00433015760095</v>
       </c>
       <c r="S4">
-        <v>-59.99916011567358</v>
+        <v>150.0030046931367</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9509,22 +9509,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8999923639797346</v>
+        <v>0.8999923639797364</v>
       </c>
       <c r="O5">
-        <v>0.8998517245861039</v>
+        <v>0.8998517245861085</v>
       </c>
       <c r="P5">
-        <v>0.8999334660935799</v>
+        <v>0.8999334660935802</v>
       </c>
       <c r="Q5">
-        <v>29.99483075058194</v>
+        <v>29.99483075058197</v>
       </c>
       <c r="R5">
-        <v>-90.00433015759731</v>
+        <v>-90.00433015759749</v>
       </c>
       <c r="S5">
-        <v>150.0030046931383</v>
+        <v>150.0030046931381</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9538,55 +9538,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.02543741345581298</v>
+        <v>0.02543741345524633</v>
       </c>
       <c r="D6">
-        <v>0.02543736038094449</v>
+        <v>0.0254373603803786</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.005874519090017728</v>
+        <v>0.005874519089886866</v>
       </c>
       <c r="G6">
-        <v>0.005874506832901701</v>
+        <v>0.005874506832771014</v>
       </c>
       <c r="H6">
-        <v>4155844.200064437</v>
+        <v>4155844.262172014</v>
       </c>
       <c r="I6">
-        <v>-0.2586079591434</v>
+        <v>-0.2586077426547335</v>
       </c>
       <c r="J6">
-        <v>0.0009575007313718255</v>
+        <v>0.0009575007810423644</v>
       </c>
       <c r="K6">
-        <v>0.006296894916599134</v>
+        <v>0.006296894790639696</v>
       </c>
       <c r="L6">
-        <v>0.0009575007180626447</v>
+        <v>0.0009575006817012867</v>
       </c>
       <c r="M6">
-        <v>0.006296894641628079</v>
+        <v>0.006296894817258057</v>
       </c>
       <c r="N6">
-        <v>0.900044676892737</v>
+        <v>0.9000446768926975</v>
       </c>
       <c r="O6">
-        <v>0.8993474258594237</v>
+        <v>0.8993474258594234</v>
       </c>
       <c r="P6">
-        <v>0.8996290408519255</v>
+        <v>0.8996290408519262</v>
       </c>
       <c r="Q6">
-        <v>29.97437218926656</v>
+        <v>29.97437218926636</v>
       </c>
       <c r="R6">
-        <v>-90.03057029446066</v>
+        <v>-90.03057029445935</v>
       </c>
       <c r="S6">
-        <v>150.0103592233241</v>
+        <v>150.0103592233225</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9645,7 +9645,7 @@
         <v>1.099978839014074</v>
       </c>
       <c r="G2">
-        <v>149.9990981575573</v>
+        <v>-0.0009018424366363309</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9665,10 +9665,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1.099893738025532</v>
+        <v>1.099893738025533</v>
       </c>
       <c r="G3">
-        <v>149.9949624247528</v>
+        <v>-0.005037575241080466</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9688,10 +9688,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1.099844930798714</v>
+        <v>1.099844930798715</v>
       </c>
       <c r="G4">
-        <v>149.9948032546806</v>
+        <v>-0.005196745313343396</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1.099844930798684</v>
+        <v>1.099844930798685</v>
       </c>
       <c r="G5">
-        <v>-0.005196745310383688</v>
+        <v>-0.00519674531033874</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9722,22 +9722,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03590070767517213</v>
+        <v>0.03590070767517219</v>
       </c>
       <c r="C6">
-        <v>0.02487274025906314</v>
+        <v>0.02487274025906318</v>
       </c>
       <c r="D6">
-        <v>0.0007617443451978032</v>
+        <v>0.0007617443451851989</v>
       </c>
       <c r="E6">
-        <v>0.006240294707275744</v>
+        <v>0.006240294707272939</v>
       </c>
       <c r="F6">
-        <v>1.099230173732585</v>
+        <v>1.099230173732587</v>
       </c>
       <c r="G6">
-        <v>44.99999999999814</v>
+        <v>44.99999999999825</v>
       </c>
     </row>
   </sheetData>
@@ -9790,10 +9790,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9202097000238783</v>
+        <v>0.9202097000230514</v>
       </c>
       <c r="G2">
-        <v>149.9048798557205</v>
+        <v>-0.09512014424988315</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9813,10 +9813,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8065751372452601</v>
+        <v>0.80657513724449</v>
       </c>
       <c r="G3">
-        <v>148.9437256189348</v>
+        <v>-1.056274381063369</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9836,10 +9836,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.7636659323891967</v>
+        <v>0.7636659323883898</v>
       </c>
       <c r="G4">
-        <v>152.9069473327529</v>
+        <v>2.906947332764131</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9859,10 +9859,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7636659324126012</v>
+        <v>0.7636659324117794</v>
       </c>
       <c r="G5">
-        <v>2.906947337496187</v>
+        <v>2.906947337501114</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9870,22 +9870,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>34.44552616790283</v>
+        <v>34.44552616794237</v>
       </c>
       <c r="C6">
-        <v>23.86456092211006</v>
+        <v>23.86456092213745</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479242149</v>
+        <v>0.0009575007479215066</v>
       </c>
       <c r="E6">
-        <v>0.006296894770926768</v>
+        <v>0.006296894770919785</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>81.35388243328349</v>
+        <v>81.35388243329812</v>
       </c>
     </row>
   </sheetData>
@@ -9938,10 +9938,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.8717775983940845</v>
+        <v>0.8717775983933012</v>
       </c>
       <c r="G2">
-        <v>149.9048798557205</v>
+        <v>-0.09512014424988338</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9961,10 +9961,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.7641238035784736</v>
+        <v>0.764123803577744</v>
       </c>
       <c r="G3">
-        <v>148.9437256189348</v>
+        <v>-1.05627438106337</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9984,10 +9984,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.7234729784921393</v>
+        <v>0.7234729784913748</v>
       </c>
       <c r="G4">
-        <v>152.9069473327529</v>
+        <v>2.90694733276413</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10007,10 +10007,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7234729785143119</v>
+        <v>0.7234729785135334</v>
       </c>
       <c r="G5">
-        <v>2.906947337496186</v>
+        <v>2.906947337501113</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10018,22 +10018,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>32.63260328302964</v>
+        <v>32.63260328306709</v>
       </c>
       <c r="C6">
-        <v>22.60853108467187</v>
+        <v>22.60853108469782</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479242149</v>
+        <v>0.0009575007479215066</v>
       </c>
       <c r="E6">
-        <v>0.006296894770926768</v>
+        <v>0.006296894770919785</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>81.35388243328349</v>
+        <v>81.35388243329812</v>
       </c>
     </row>
   </sheetData>
@@ -10086,10 +10086,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9499791979636301</v>
+        <v>0.9499791979636297</v>
       </c>
       <c r="G2">
-        <v>149.9989751847345</v>
+        <v>-0.001024815259467744</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10109,10 +10109,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.9499038087630102</v>
+        <v>0.9499038087630096</v>
       </c>
       <c r="G3">
-        <v>149.9947327763505</v>
+        <v>-0.005267223643389584</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10132,10 +10132,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.9498435003064272</v>
+        <v>0.9498435003064266</v>
       </c>
       <c r="G4">
-        <v>149.9956698423893</v>
+        <v>-0.004330157604604892</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10155,10 +10155,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.9498435003064076</v>
+        <v>0.9498435003064071</v>
       </c>
       <c r="G5">
-        <v>-0.00433015760116278</v>
+        <v>-0.004330157601146439</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10166,19 +10166,19 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.03100437393278748</v>
+        <v>0.03100437393278751</v>
       </c>
       <c r="C6">
-        <v>0.0214804606834646</v>
+        <v>0.02148046068346462</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479242149</v>
+        <v>0.0009575007479215066</v>
       </c>
       <c r="E6">
-        <v>0.006296894770926768</v>
+        <v>0.006296894770919785</v>
       </c>
       <c r="F6">
-        <v>0.9493111849763747</v>
+        <v>0.9493111849763752</v>
       </c>
       <c r="G6">
         <v>44.99999999999817</v>
@@ -10234,10 +10234,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.8999802802595779</v>
+        <v>0.8999802802595775</v>
       </c>
       <c r="G2">
-        <v>149.9989751847345</v>
+        <v>-0.001024815259467744</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10257,10 +10257,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8999088589126178</v>
+        <v>0.8999088589126175</v>
       </c>
       <c r="G3">
-        <v>149.9947327763505</v>
+        <v>-0.005267223643389584</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10280,10 +10280,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.8998517245861254</v>
+        <v>0.8998517245861249</v>
       </c>
       <c r="G4">
-        <v>149.9956698423893</v>
+        <v>-0.004330157604604892</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10303,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8998517245861068</v>
+        <v>0.8998517245861064</v>
       </c>
       <c r="G5">
-        <v>-0.00433015760116278</v>
+        <v>-0.00433015760114644</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10314,19 +10314,19 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.02937256436890011</v>
+        <v>0.02937256436890014</v>
       </c>
       <c r="C6">
-        <v>0.02034990983744619</v>
+        <v>0.02034990983744621</v>
       </c>
       <c r="D6">
-        <v>0.0009575007479242149</v>
+        <v>0.0009575007479215066</v>
       </c>
       <c r="E6">
-        <v>0.006296894770926768</v>
+        <v>0.006296894770919785</v>
       </c>
       <c r="F6">
-        <v>0.8993474258594228</v>
+        <v>0.8993474258594233</v>
       </c>
       <c r="G6">
         <v>44.99999999999816</v>
@@ -10442,22 +10442,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049999952315168</v>
+        <v>1.042756081987974</v>
       </c>
       <c r="O2">
-        <v>1.027504579962663</v>
+        <v>1.019485521633547</v>
       </c>
       <c r="P2">
-        <v>1.02689355906545</v>
+        <v>1.042154003821248</v>
       </c>
       <c r="Q2">
-        <v>179.9999999999575</v>
+        <v>29.26447752933257</v>
       </c>
       <c r="R2">
-        <v>59.23431350239034</v>
+        <v>-90.03879108304258</v>
       </c>
       <c r="S2">
-        <v>-59.29162958514361</v>
+        <v>150.7169722416111</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -10501,22 +10501,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049999952313864</v>
+        <v>1.01785081498351</v>
       </c>
       <c r="O3">
-        <v>0.938630272435748</v>
+        <v>0.8902319384054118</v>
       </c>
       <c r="P3">
-        <v>0.9268184935802718</v>
+        <v>1.006968728564998</v>
       </c>
       <c r="Q3">
-        <v>179.9999999999163</v>
+        <v>25.92977055595862</v>
       </c>
       <c r="R3">
-        <v>55.21460939109824</v>
+        <v>-90.77979681429257</v>
       </c>
       <c r="S3">
-        <v>-56.28012876510495</v>
+        <v>153.7687858474697</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -10560,22 +10560,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049999952313864</v>
+        <v>0.9942448475740322</v>
       </c>
       <c r="O4">
-        <v>0.8913852196409775</v>
+        <v>0.8453339436438737</v>
       </c>
       <c r="P4">
-        <v>0.9102563126204283</v>
+        <v>1.011198185818496</v>
       </c>
       <c r="Q4">
-        <v>179.9999999999163</v>
+        <v>25.15127083811544</v>
       </c>
       <c r="R4">
-        <v>55.1933960547149</v>
+        <v>-88.73279936686531</v>
       </c>
       <c r="S4">
-        <v>-53.51967089073337</v>
+        <v>155.2989288667105</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -10619,22 +10619,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.994244849869408</v>
+        <v>0.9942448475461818</v>
       </c>
       <c r="O5">
-        <v>0.8453339437039747</v>
+        <v>0.8453339436584665</v>
       </c>
       <c r="P5">
-        <v>1.011198183585143</v>
+        <v>1.011198185851979</v>
       </c>
       <c r="Q5">
-        <v>25.15127078136157</v>
+        <v>25.15127083928597</v>
       </c>
       <c r="R5">
-        <v>-88.73279970555232</v>
+        <v>-88.73279936229842</v>
       </c>
       <c r="S5">
-        <v>155.2989288031085</v>
+        <v>155.2989288671747</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -10645,55 +10645,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>34.68462511716788</v>
+        <v>34.68462522131649</v>
       </c>
       <c r="D6">
-        <v>34.68462511716788</v>
+        <v>34.68462522131649</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>8.010071178614615</v>
+        <v>8.010071202666705</v>
       </c>
       <c r="G6">
-        <v>8.010071178614615</v>
+        <v>8.010071202666705</v>
       </c>
       <c r="H6">
-        <v>4155844.2130444</v>
+        <v>4155844.289159183</v>
       </c>
       <c r="I6">
-        <v>0.3382144411803715</v>
+        <v>-0.09667844596139809</v>
       </c>
       <c r="J6">
-        <v>0.000738532876650268</v>
+        <v>0.0007385327476024228</v>
       </c>
       <c r="K6">
-        <v>0.006009343808324313</v>
+        <v>0.006009344031841738</v>
       </c>
       <c r="L6">
-        <v>0.0007385329263208069</v>
+        <v>0.000738533019007294</v>
       </c>
       <c r="M6">
-        <v>0.006009343672621878</v>
+        <v>0.006009343634477428</v>
       </c>
       <c r="N6">
-        <v>0.9093266414689568</v>
+        <v>0.9093266286441974</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9093266238835315</v>
+        <v>0.9093266367092009</v>
       </c>
       <c r="Q6">
-        <v>6.800154137062591E-08</v>
+        <v>-3.123035228912993E-08</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999318291</v>
+        <v>-179.9999999687638</v>
       </c>
     </row>
   </sheetData>
